--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373465</v>
+        <v>129373408</v>
       </c>
       <c r="B2" t="n">
-        <v>98605</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663295</v>
+        <v>663316</v>
       </c>
       <c r="R2" t="n">
-        <v>6987442</v>
+        <v>6987426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373408</v>
+        <v>129373465</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>98621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663316</v>
+        <v>663295</v>
       </c>
       <c r="R3" t="n">
-        <v>6987426</v>
+        <v>6987442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1066,7 +1066,7 @@
         <v>129373403</v>
       </c>
       <c r="B6" t="n">
-        <v>91543</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373402</v>
       </c>
       <c r="B10" t="n">
-        <v>91543</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129373443</v>
       </c>
       <c r="B13" t="n">
-        <v>92874</v>
+        <v>92859</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373410</v>
+        <v>129373473</v>
       </c>
       <c r="B14" t="n">
-        <v>91543</v>
+        <v>88940</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663058</v>
+        <v>663293</v>
       </c>
       <c r="R14" t="n">
-        <v>6986973</v>
+        <v>6987424</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373473</v>
+        <v>129373410</v>
       </c>
       <c r="B15" t="n">
-        <v>88940</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663293</v>
+        <v>663058</v>
       </c>
       <c r="R15" t="n">
-        <v>6987424</v>
+        <v>6986973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129373460</v>
+        <v>129373425</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>663293</v>
+        <v>663240</v>
       </c>
       <c r="R17" t="n">
-        <v>6987423</v>
+        <v>6987407</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129373455</v>
+        <v>129373460</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>663366</v>
+        <v>663293</v>
       </c>
       <c r="R18" t="n">
-        <v>6987548</v>
+        <v>6987423</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129373425</v>
+        <v>129373455</v>
       </c>
       <c r="B19" t="n">
-        <v>79108</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>663240</v>
+        <v>663366</v>
       </c>
       <c r="R19" t="n">
-        <v>6987407</v>
+        <v>6987548</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373408</v>
+        <v>129373465</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>98622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663316</v>
+        <v>663295</v>
       </c>
       <c r="R2" t="n">
-        <v>6987426</v>
+        <v>6987442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373465</v>
+        <v>129373408</v>
       </c>
       <c r="B3" t="n">
-        <v>98621</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663295</v>
+        <v>663316</v>
       </c>
       <c r="R3" t="n">
-        <v>6987442</v>
+        <v>6987426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129373475</v>
+        <v>129373403</v>
       </c>
       <c r="B5" t="n">
-        <v>78444</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663432</v>
+        <v>663376</v>
       </c>
       <c r="R5" t="n">
-        <v>6987778</v>
+        <v>6987579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129373403</v>
+        <v>129373475</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>78444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663376</v>
+        <v>663432</v>
       </c>
       <c r="R6" t="n">
-        <v>6987579</v>
+        <v>6987778</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>129373443</v>
       </c>
       <c r="B13" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373465</v>
       </c>
       <c r="B2" t="n">
-        <v>98622</v>
+        <v>98623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373473</v>
+        <v>129373410</v>
       </c>
       <c r="B14" t="n">
-        <v>88940</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663293</v>
+        <v>663058</v>
       </c>
       <c r="R14" t="n">
-        <v>6987424</v>
+        <v>6986973</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373410</v>
+        <v>129373473</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>88940</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663058</v>
+        <v>663293</v>
       </c>
       <c r="R15" t="n">
-        <v>6986973</v>
+        <v>6987424</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129373460</v>
+        <v>129373455</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>663293</v>
+        <v>663366</v>
       </c>
       <c r="R18" t="n">
-        <v>6987423</v>
+        <v>6987548</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129373455</v>
+        <v>129373460</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>663366</v>
+        <v>663293</v>
       </c>
       <c r="R19" t="n">
-        <v>6987548</v>
+        <v>6987423</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373465</v>
+        <v>129373408</v>
       </c>
       <c r="B2" t="n">
-        <v>98623</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663295</v>
+        <v>663316</v>
       </c>
       <c r="R2" t="n">
-        <v>6987442</v>
+        <v>6987426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373408</v>
+        <v>129373465</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>98627</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663316</v>
+        <v>663295</v>
       </c>
       <c r="R3" t="n">
-        <v>6987426</v>
+        <v>6987442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,7 +872,7 @@
         <v>129373423</v>
       </c>
       <c r="B4" t="n">
-        <v>79108</v>
+        <v>79110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373403</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373475</v>
       </c>
       <c r="B6" t="n">
-        <v>78444</v>
+        <v>78446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129373424</v>
       </c>
       <c r="B7" t="n">
-        <v>79108</v>
+        <v>79110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129373445</v>
       </c>
       <c r="B8" t="n">
-        <v>81026</v>
+        <v>81028</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129373470</v>
       </c>
       <c r="B9" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373402</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129373397</v>
       </c>
       <c r="B11" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129373422</v>
       </c>
       <c r="B12" t="n">
-        <v>79108</v>
+        <v>79110</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129373443</v>
       </c>
       <c r="B13" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129373410</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>129373473</v>
       </c>
       <c r="B15" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>129373474</v>
       </c>
       <c r="B16" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129373425</v>
       </c>
       <c r="B17" t="n">
-        <v>79108</v>
+        <v>79110</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129373455</v>
+        <v>129373460</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>663366</v>
+        <v>663293</v>
       </c>
       <c r="R18" t="n">
-        <v>6987548</v>
+        <v>6987423</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129373460</v>
+        <v>129373455</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>663293</v>
+        <v>663366</v>
       </c>
       <c r="R19" t="n">
-        <v>6987423</v>
+        <v>6987548</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2424,7 +2424,7 @@
         <v>129373456</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129373471</v>
       </c>
       <c r="B21" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373408</v>
+        <v>129373465</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>98629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663316</v>
+        <v>663295</v>
       </c>
       <c r="R2" t="n">
-        <v>6987426</v>
+        <v>6987442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373465</v>
+        <v>129373408</v>
       </c>
       <c r="B3" t="n">
-        <v>98627</v>
+        <v>91545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663295</v>
+        <v>663316</v>
       </c>
       <c r="R3" t="n">
-        <v>6987442</v>
+        <v>6987426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,7 +872,7 @@
         <v>129373423</v>
       </c>
       <c r="B4" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373403</v>
       </c>
       <c r="B5" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373475</v>
       </c>
       <c r="B6" t="n">
-        <v>78446</v>
+        <v>78447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129373424</v>
       </c>
       <c r="B7" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129373445</v>
       </c>
       <c r="B8" t="n">
-        <v>81028</v>
+        <v>81029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129373470</v>
       </c>
       <c r="B9" t="n">
-        <v>88943</v>
+        <v>88945</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373402</v>
       </c>
       <c r="B10" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129373397</v>
       </c>
       <c r="B11" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129373422</v>
       </c>
       <c r="B12" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129373443</v>
       </c>
       <c r="B13" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373410</v>
+        <v>129373473</v>
       </c>
       <c r="B14" t="n">
-        <v>91543</v>
+        <v>88945</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663058</v>
+        <v>663293</v>
       </c>
       <c r="R14" t="n">
-        <v>6986973</v>
+        <v>6987424</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373473</v>
+        <v>129373410</v>
       </c>
       <c r="B15" t="n">
-        <v>88943</v>
+        <v>91545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663293</v>
+        <v>663058</v>
       </c>
       <c r="R15" t="n">
-        <v>6987424</v>
+        <v>6986973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>129373474</v>
       </c>
       <c r="B16" t="n">
-        <v>88943</v>
+        <v>88945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129373425</v>
       </c>
       <c r="B17" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>129373460</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>129373455</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>129373456</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129373471</v>
       </c>
       <c r="B21" t="n">
-        <v>88943</v>
+        <v>88945</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373465</v>
+        <v>129373408</v>
       </c>
       <c r="B2" t="n">
-        <v>98629</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663295</v>
+        <v>663316</v>
       </c>
       <c r="R2" t="n">
-        <v>6987442</v>
+        <v>6987426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373408</v>
+        <v>129373465</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>98633</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663316</v>
+        <v>663295</v>
       </c>
       <c r="R3" t="n">
-        <v>6987426</v>
+        <v>6987442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -969,7 +969,7 @@
         <v>129373403</v>
       </c>
       <c r="B5" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129373470</v>
       </c>
       <c r="B9" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373402</v>
       </c>
       <c r="B10" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129373443</v>
       </c>
       <c r="B13" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129373473</v>
       </c>
       <c r="B14" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>129373410</v>
       </c>
       <c r="B15" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>129373474</v>
       </c>
       <c r="B16" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129373471</v>
       </c>
       <c r="B21" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373408</v>
       </c>
       <c r="B2" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129373465</v>
       </c>
       <c r="B3" t="n">
-        <v>98633</v>
+        <v>98641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373403</v>
       </c>
       <c r="B5" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129373470</v>
       </c>
       <c r="B9" t="n">
-        <v>88949</v>
+        <v>88950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373402</v>
       </c>
       <c r="B10" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129373443</v>
       </c>
       <c r="B13" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129373473</v>
       </c>
       <c r="B14" t="n">
-        <v>88949</v>
+        <v>88950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>129373410</v>
       </c>
       <c r="B15" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>129373474</v>
       </c>
       <c r="B16" t="n">
-        <v>88949</v>
+        <v>88950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129373471</v>
       </c>
       <c r="B21" t="n">
-        <v>88949</v>
+        <v>88950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373473</v>
+        <v>129373410</v>
       </c>
       <c r="B14" t="n">
-        <v>88950</v>
+        <v>91550</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663293</v>
+        <v>663058</v>
       </c>
       <c r="R14" t="n">
-        <v>6987424</v>
+        <v>6986973</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373410</v>
+        <v>129373473</v>
       </c>
       <c r="B15" t="n">
-        <v>91550</v>
+        <v>88950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663058</v>
+        <v>663293</v>
       </c>
       <c r="R15" t="n">
-        <v>6986973</v>
+        <v>6987424</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129373425</v>
+        <v>129373460</v>
       </c>
       <c r="B17" t="n">
-        <v>79111</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>663240</v>
+        <v>663293</v>
       </c>
       <c r="R17" t="n">
-        <v>6987407</v>
+        <v>6987423</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129373460</v>
+        <v>129373455</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>663293</v>
+        <v>663366</v>
       </c>
       <c r="R18" t="n">
-        <v>6987423</v>
+        <v>6987548</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129373455</v>
+        <v>129373425</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79111</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>663366</v>
+        <v>663240</v>
       </c>
       <c r="R19" t="n">
-        <v>6987548</v>
+        <v>6987407</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373408</v>
+        <v>129373465</v>
       </c>
       <c r="B2" t="n">
-        <v>91550</v>
+        <v>98644</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663316</v>
+        <v>663295</v>
       </c>
       <c r="R2" t="n">
-        <v>6987426</v>
+        <v>6987442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373465</v>
+        <v>129373408</v>
       </c>
       <c r="B3" t="n">
-        <v>98641</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663295</v>
+        <v>663316</v>
       </c>
       <c r="R3" t="n">
-        <v>6987442</v>
+        <v>6987426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -969,7 +969,7 @@
         <v>129373403</v>
       </c>
       <c r="B5" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129373470</v>
       </c>
       <c r="B9" t="n">
-        <v>88950</v>
+        <v>88952</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373402</v>
       </c>
       <c r="B10" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129373443</v>
       </c>
       <c r="B13" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129373410</v>
       </c>
       <c r="B14" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>129373473</v>
       </c>
       <c r="B15" t="n">
-        <v>88950</v>
+        <v>88952</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>129373474</v>
       </c>
       <c r="B16" t="n">
-        <v>88950</v>
+        <v>88952</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129373460</v>
+        <v>129373425</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79111</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>663293</v>
+        <v>663240</v>
       </c>
       <c r="R17" t="n">
-        <v>6987423</v>
+        <v>6987407</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129373425</v>
+        <v>129373460</v>
       </c>
       <c r="B19" t="n">
-        <v>79111</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>663240</v>
+        <v>663293</v>
       </c>
       <c r="R19" t="n">
-        <v>6987407</v>
+        <v>6987423</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,7 +2521,7 @@
         <v>129373471</v>
       </c>
       <c r="B21" t="n">
-        <v>88950</v>
+        <v>88952</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373465</v>
+        <v>129373408</v>
       </c>
       <c r="B2" t="n">
-        <v>98644</v>
+        <v>91553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663295</v>
+        <v>663316</v>
       </c>
       <c r="R2" t="n">
-        <v>6987442</v>
+        <v>6987426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373408</v>
+        <v>129373465</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>98644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663316</v>
+        <v>663295</v>
       </c>
       <c r="R3" t="n">
-        <v>6987426</v>
+        <v>6987442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373410</v>
+        <v>129373473</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>88952</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663058</v>
+        <v>663293</v>
       </c>
       <c r="R14" t="n">
-        <v>6986973</v>
+        <v>6987424</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373473</v>
+        <v>129373410</v>
       </c>
       <c r="B15" t="n">
-        <v>88952</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663293</v>
+        <v>663058</v>
       </c>
       <c r="R15" t="n">
-        <v>6987424</v>
+        <v>6986973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129373425</v>
+        <v>129373460</v>
       </c>
       <c r="B17" t="n">
-        <v>79111</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>663240</v>
+        <v>663293</v>
       </c>
       <c r="R17" t="n">
-        <v>6987407</v>
+        <v>6987423</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129373460</v>
+        <v>129373425</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79111</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>663293</v>
+        <v>663240</v>
       </c>
       <c r="R19" t="n">
-        <v>6987423</v>
+        <v>6987407</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373473</v>
+        <v>129373410</v>
       </c>
       <c r="B14" t="n">
-        <v>88952</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663293</v>
+        <v>663058</v>
       </c>
       <c r="R14" t="n">
-        <v>6987424</v>
+        <v>6986973</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373410</v>
+        <v>129373473</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>88952</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663058</v>
+        <v>663293</v>
       </c>
       <c r="R15" t="n">
-        <v>6986973</v>
+        <v>6987424</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129373460</v>
+        <v>129373425</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79111</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>663293</v>
+        <v>663240</v>
       </c>
       <c r="R17" t="n">
-        <v>6987423</v>
+        <v>6987407</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129373425</v>
+        <v>129373460</v>
       </c>
       <c r="B19" t="n">
-        <v>79111</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>663240</v>
+        <v>663293</v>
       </c>
       <c r="R19" t="n">
-        <v>6987407</v>
+        <v>6987423</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373408</v>
+        <v>129373465</v>
       </c>
       <c r="B2" t="n">
-        <v>91553</v>
+        <v>98644</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663316</v>
+        <v>663295</v>
       </c>
       <c r="R2" t="n">
-        <v>6987426</v>
+        <v>6987442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373465</v>
+        <v>129373408</v>
       </c>
       <c r="B3" t="n">
-        <v>98644</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663295</v>
+        <v>663316</v>
       </c>
       <c r="R3" t="n">
-        <v>6987442</v>
+        <v>6987426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129373403</v>
+        <v>129373475</v>
       </c>
       <c r="B5" t="n">
-        <v>91553</v>
+        <v>78447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663376</v>
+        <v>663432</v>
       </c>
       <c r="R5" t="n">
-        <v>6987579</v>
+        <v>6987778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129373475</v>
+        <v>129373403</v>
       </c>
       <c r="B6" t="n">
-        <v>78447</v>
+        <v>91553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663432</v>
+        <v>663376</v>
       </c>
       <c r="R6" t="n">
-        <v>6987778</v>
+        <v>6987579</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373410</v>
+        <v>129373473</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>88952</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663058</v>
+        <v>663293</v>
       </c>
       <c r="R14" t="n">
-        <v>6986973</v>
+        <v>6987424</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373473</v>
+        <v>129373410</v>
       </c>
       <c r="B15" t="n">
-        <v>88952</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663293</v>
+        <v>663058</v>
       </c>
       <c r="R15" t="n">
-        <v>6987424</v>
+        <v>6986973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129373455</v>
+        <v>129373460</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>663366</v>
+        <v>663293</v>
       </c>
       <c r="R18" t="n">
-        <v>6987548</v>
+        <v>6987423</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129373460</v>
+        <v>129373455</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>663293</v>
+        <v>663366</v>
       </c>
       <c r="R19" t="n">
-        <v>6987423</v>
+        <v>6987548</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373465</v>
+        <v>129373408</v>
       </c>
       <c r="B2" t="n">
-        <v>98644</v>
+        <v>91553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663295</v>
+        <v>663316</v>
       </c>
       <c r="R2" t="n">
-        <v>6987442</v>
+        <v>6987426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373408</v>
+        <v>129373465</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>98644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663316</v>
+        <v>663295</v>
       </c>
       <c r="R3" t="n">
-        <v>6987426</v>
+        <v>6987442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373473</v>
+        <v>129373410</v>
       </c>
       <c r="B14" t="n">
-        <v>88952</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663293</v>
+        <v>663058</v>
       </c>
       <c r="R14" t="n">
-        <v>6987424</v>
+        <v>6986973</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373410</v>
+        <v>129373473</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>88952</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663058</v>
+        <v>663293</v>
       </c>
       <c r="R15" t="n">
-        <v>6986973</v>
+        <v>6987424</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373408</v>
+        <v>129373465</v>
       </c>
       <c r="B2" t="n">
-        <v>91553</v>
+        <v>98644</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663316</v>
+        <v>663295</v>
       </c>
       <c r="R2" t="n">
-        <v>6987426</v>
+        <v>6987442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373465</v>
+        <v>129373408</v>
       </c>
       <c r="B3" t="n">
-        <v>98644</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663295</v>
+        <v>663316</v>
       </c>
       <c r="R3" t="n">
-        <v>6987442</v>
+        <v>6987426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129373475</v>
+        <v>129373403</v>
       </c>
       <c r="B5" t="n">
-        <v>78447</v>
+        <v>91553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663432</v>
+        <v>663376</v>
       </c>
       <c r="R5" t="n">
-        <v>6987778</v>
+        <v>6987579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129373403</v>
+        <v>129373475</v>
       </c>
       <c r="B6" t="n">
-        <v>91553</v>
+        <v>78447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663376</v>
+        <v>663432</v>
       </c>
       <c r="R6" t="n">
-        <v>6987579</v>
+        <v>6987778</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373465</v>
+        <v>129373408</v>
       </c>
       <c r="B2" t="n">
-        <v>98644</v>
+        <v>91581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663295</v>
+        <v>663316</v>
       </c>
       <c r="R2" t="n">
-        <v>6987442</v>
+        <v>6987426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373408</v>
+        <v>129373465</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>98673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663316</v>
+        <v>663295</v>
       </c>
       <c r="R3" t="n">
-        <v>6987426</v>
+        <v>6987442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,7 +872,7 @@
         <v>129373423</v>
       </c>
       <c r="B4" t="n">
-        <v>79111</v>
+        <v>79137</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373403</v>
       </c>
       <c r="B5" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373475</v>
       </c>
       <c r="B6" t="n">
-        <v>78447</v>
+        <v>78473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129373424</v>
       </c>
       <c r="B7" t="n">
-        <v>79111</v>
+        <v>79137</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129373445</v>
       </c>
       <c r="B8" t="n">
-        <v>81029</v>
+        <v>81055</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129373470</v>
       </c>
       <c r="B9" t="n">
-        <v>88952</v>
+        <v>88980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373402</v>
       </c>
       <c r="B10" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129373397</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129373422</v>
       </c>
       <c r="B12" t="n">
-        <v>79111</v>
+        <v>79137</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129373443</v>
       </c>
       <c r="B13" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129373410</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>129373473</v>
       </c>
       <c r="B15" t="n">
-        <v>88952</v>
+        <v>88980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>129373474</v>
       </c>
       <c r="B16" t="n">
-        <v>88952</v>
+        <v>88980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129373425</v>
       </c>
       <c r="B17" t="n">
-        <v>79111</v>
+        <v>79137</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129373460</v>
+        <v>129373455</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>663293</v>
+        <v>663366</v>
       </c>
       <c r="R18" t="n">
-        <v>6987423</v>
+        <v>6987548</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129373455</v>
+        <v>129373460</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>663366</v>
+        <v>663293</v>
       </c>
       <c r="R19" t="n">
-        <v>6987548</v>
+        <v>6987423</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2424,7 +2424,7 @@
         <v>129373456</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129373471</v>
       </c>
       <c r="B21" t="n">
-        <v>88952</v>
+        <v>88980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129373455</v>
+        <v>129373460</v>
       </c>
       <c r="B18" t="n">
         <v>79070</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>663366</v>
+        <v>663293</v>
       </c>
       <c r="R18" t="n">
-        <v>6987548</v>
+        <v>6987423</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129373460</v>
+        <v>129373455</v>
       </c>
       <c r="B19" t="n">
         <v>79070</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>663293</v>
+        <v>663366</v>
       </c>
       <c r="R19" t="n">
-        <v>6987423</v>
+        <v>6987548</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373408</v>
+        <v>129373465</v>
       </c>
       <c r="B2" t="n">
-        <v>91581</v>
+        <v>98685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663316</v>
+        <v>663295</v>
       </c>
       <c r="R2" t="n">
-        <v>6987426</v>
+        <v>6987442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373465</v>
+        <v>129373408</v>
       </c>
       <c r="B3" t="n">
-        <v>98673</v>
+        <v>91587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663295</v>
+        <v>663316</v>
       </c>
       <c r="R3" t="n">
-        <v>6987442</v>
+        <v>6987426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,7 +872,7 @@
         <v>129373423</v>
       </c>
       <c r="B4" t="n">
-        <v>79137</v>
+        <v>79142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373403</v>
       </c>
       <c r="B5" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373475</v>
       </c>
       <c r="B6" t="n">
-        <v>78473</v>
+        <v>78478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129373424</v>
       </c>
       <c r="B7" t="n">
-        <v>79137</v>
+        <v>79142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129373445</v>
       </c>
       <c r="B8" t="n">
-        <v>81055</v>
+        <v>81060</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129373470</v>
       </c>
       <c r="B9" t="n">
-        <v>88980</v>
+        <v>88986</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373402</v>
       </c>
       <c r="B10" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129373397</v>
       </c>
       <c r="B11" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129373422</v>
       </c>
       <c r="B12" t="n">
-        <v>79137</v>
+        <v>79142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129373443</v>
       </c>
       <c r="B13" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373410</v>
+        <v>129373473</v>
       </c>
       <c r="B14" t="n">
-        <v>91581</v>
+        <v>88986</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663058</v>
+        <v>663293</v>
       </c>
       <c r="R14" t="n">
-        <v>6986973</v>
+        <v>6987424</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373473</v>
+        <v>129373410</v>
       </c>
       <c r="B15" t="n">
-        <v>88980</v>
+        <v>91587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663293</v>
+        <v>663058</v>
       </c>
       <c r="R15" t="n">
-        <v>6987424</v>
+        <v>6986973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>129373474</v>
       </c>
       <c r="B16" t="n">
-        <v>88980</v>
+        <v>88986</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129373425</v>
+        <v>129373460</v>
       </c>
       <c r="B17" t="n">
-        <v>79137</v>
+        <v>79075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>663240</v>
+        <v>663293</v>
       </c>
       <c r="R17" t="n">
-        <v>6987407</v>
+        <v>6987423</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129373460</v>
+        <v>129373425</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>79142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>663293</v>
+        <v>663240</v>
       </c>
       <c r="R18" t="n">
-        <v>6987423</v>
+        <v>6987407</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2327,7 +2327,7 @@
         <v>129373455</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>129373456</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129373471</v>
       </c>
       <c r="B21" t="n">
-        <v>88980</v>
+        <v>88986</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373465</v>
+        <v>129373408</v>
       </c>
       <c r="B2" t="n">
-        <v>98685</v>
+        <v>91588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663295</v>
+        <v>663316</v>
       </c>
       <c r="R2" t="n">
-        <v>6987442</v>
+        <v>6987426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373408</v>
+        <v>129373465</v>
       </c>
       <c r="B3" t="n">
-        <v>91587</v>
+        <v>98686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663316</v>
+        <v>663295</v>
       </c>
       <c r="R3" t="n">
-        <v>6987426</v>
+        <v>6987442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,7 +872,7 @@
         <v>129373423</v>
       </c>
       <c r="B4" t="n">
-        <v>79142</v>
+        <v>79143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129373403</v>
+        <v>129373475</v>
       </c>
       <c r="B5" t="n">
-        <v>91587</v>
+        <v>78479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663376</v>
+        <v>663432</v>
       </c>
       <c r="R5" t="n">
-        <v>6987579</v>
+        <v>6987778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129373475</v>
+        <v>129373403</v>
       </c>
       <c r="B6" t="n">
-        <v>78478</v>
+        <v>91588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663432</v>
+        <v>663376</v>
       </c>
       <c r="R6" t="n">
-        <v>6987778</v>
+        <v>6987579</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>129373424</v>
       </c>
       <c r="B7" t="n">
-        <v>79142</v>
+        <v>79143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129373445</v>
       </c>
       <c r="B8" t="n">
-        <v>81060</v>
+        <v>81061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129373470</v>
       </c>
       <c r="B9" t="n">
-        <v>88986</v>
+        <v>88987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373402</v>
       </c>
       <c r="B10" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129373397</v>
       </c>
       <c r="B11" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129373422</v>
       </c>
       <c r="B12" t="n">
-        <v>79142</v>
+        <v>79143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129373443</v>
       </c>
       <c r="B13" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373473</v>
+        <v>129373410</v>
       </c>
       <c r="B14" t="n">
-        <v>88986</v>
+        <v>91588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663293</v>
+        <v>663058</v>
       </c>
       <c r="R14" t="n">
-        <v>6987424</v>
+        <v>6986973</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373410</v>
+        <v>129373473</v>
       </c>
       <c r="B15" t="n">
-        <v>91587</v>
+        <v>88987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663058</v>
+        <v>663293</v>
       </c>
       <c r="R15" t="n">
-        <v>6986973</v>
+        <v>6987424</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>129373474</v>
       </c>
       <c r="B16" t="n">
-        <v>88986</v>
+        <v>88987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129373460</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129373425</v>
+        <v>129373455</v>
       </c>
       <c r="B18" t="n">
-        <v>79142</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>663240</v>
+        <v>663366</v>
       </c>
       <c r="R18" t="n">
-        <v>6987407</v>
+        <v>6987548</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129373455</v>
+        <v>129373425</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>79143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>663366</v>
+        <v>663240</v>
       </c>
       <c r="R19" t="n">
-        <v>6987548</v>
+        <v>6987407</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
         <v>129373456</v>
       </c>
       <c r="B20" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129373471</v>
       </c>
       <c r="B21" t="n">
-        <v>88986</v>
+        <v>88987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129373475</v>
+        <v>129373403</v>
       </c>
       <c r="B5" t="n">
-        <v>78479</v>
+        <v>91588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663432</v>
+        <v>663376</v>
       </c>
       <c r="R5" t="n">
-        <v>6987778</v>
+        <v>6987579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129373403</v>
+        <v>129373475</v>
       </c>
       <c r="B6" t="n">
-        <v>91588</v>
+        <v>78479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663376</v>
+        <v>663432</v>
       </c>
       <c r="R6" t="n">
-        <v>6987579</v>
+        <v>6987778</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373408</v>
       </c>
       <c r="B2" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129373465</v>
       </c>
       <c r="B3" t="n">
-        <v>98686</v>
+        <v>98691</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129373423</v>
       </c>
       <c r="B4" t="n">
-        <v>79143</v>
+        <v>79148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373403</v>
       </c>
       <c r="B5" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373475</v>
       </c>
       <c r="B6" t="n">
-        <v>78479</v>
+        <v>78484</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129373424</v>
       </c>
       <c r="B7" t="n">
-        <v>79143</v>
+        <v>79148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129373445</v>
       </c>
       <c r="B8" t="n">
-        <v>81061</v>
+        <v>81066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129373470</v>
       </c>
       <c r="B9" t="n">
-        <v>88987</v>
+        <v>88992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129373402</v>
       </c>
       <c r="B10" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129373397</v>
       </c>
       <c r="B11" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129373422</v>
       </c>
       <c r="B12" t="n">
-        <v>79143</v>
+        <v>79148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129373443</v>
       </c>
       <c r="B13" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373410</v>
+        <v>129373473</v>
       </c>
       <c r="B14" t="n">
-        <v>91588</v>
+        <v>88992</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663058</v>
+        <v>663293</v>
       </c>
       <c r="R14" t="n">
-        <v>6986973</v>
+        <v>6987424</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373473</v>
+        <v>129373410</v>
       </c>
       <c r="B15" t="n">
-        <v>88987</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663293</v>
+        <v>663058</v>
       </c>
       <c r="R15" t="n">
-        <v>6987424</v>
+        <v>6986973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>129373474</v>
       </c>
       <c r="B16" t="n">
-        <v>88987</v>
+        <v>88992</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129373460</v>
+        <v>129373425</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>79148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>663293</v>
+        <v>663240</v>
       </c>
       <c r="R17" t="n">
-        <v>6987423</v>
+        <v>6987407</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129373455</v>
+        <v>129373460</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>663366</v>
+        <v>663293</v>
       </c>
       <c r="R18" t="n">
-        <v>6987548</v>
+        <v>6987423</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129373425</v>
+        <v>129373455</v>
       </c>
       <c r="B19" t="n">
-        <v>79143</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>663240</v>
+        <v>663366</v>
       </c>
       <c r="R19" t="n">
-        <v>6987407</v>
+        <v>6987548</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
         <v>129373456</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129373471</v>
       </c>
       <c r="B21" t="n">
-        <v>88987</v>
+        <v>88992</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129373403</v>
+        <v>129373475</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>78484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663376</v>
+        <v>663432</v>
       </c>
       <c r="R5" t="n">
-        <v>6987579</v>
+        <v>6987778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129373475</v>
+        <v>129373403</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663432</v>
+        <v>663376</v>
       </c>
       <c r="R6" t="n">
-        <v>6987778</v>
+        <v>6987579</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373473</v>
+        <v>129373410</v>
       </c>
       <c r="B14" t="n">
-        <v>88992</v>
+        <v>91593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663293</v>
+        <v>663058</v>
       </c>
       <c r="R14" t="n">
-        <v>6987424</v>
+        <v>6986973</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373410</v>
+        <v>129373473</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>88992</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663058</v>
+        <v>663293</v>
       </c>
       <c r="R15" t="n">
-        <v>6986973</v>
+        <v>6987424</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129373425</v>
+        <v>129373460</v>
       </c>
       <c r="B17" t="n">
-        <v>79148</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>663240</v>
+        <v>663293</v>
       </c>
       <c r="R17" t="n">
-        <v>6987407</v>
+        <v>6987423</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129373460</v>
+        <v>129373455</v>
       </c>
       <c r="B18" t="n">
         <v>79081</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>663293</v>
+        <v>663366</v>
       </c>
       <c r="R18" t="n">
-        <v>6987423</v>
+        <v>6987548</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129373455</v>
+        <v>129373425</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>79148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>663366</v>
+        <v>663240</v>
       </c>
       <c r="R19" t="n">
-        <v>6987548</v>
+        <v>6987407</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 44496-2025 artfynd.xlsx
+++ b/artfynd/A 44496-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373408</v>
+        <v>129373465</v>
       </c>
       <c r="B2" t="n">
-        <v>91593</v>
+        <v>98691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663316</v>
+        <v>663295</v>
       </c>
       <c r="R2" t="n">
-        <v>6987426</v>
+        <v>6987442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373465</v>
+        <v>129373408</v>
       </c>
       <c r="B3" t="n">
-        <v>98691</v>
+        <v>91593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663295</v>
+        <v>663316</v>
       </c>
       <c r="R3" t="n">
-        <v>6987442</v>
+        <v>6987426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129373410</v>
+        <v>129373473</v>
       </c>
       <c r="B14" t="n">
-        <v>91593</v>
+        <v>88992</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663058</v>
+        <v>663293</v>
       </c>
       <c r="R14" t="n">
-        <v>6986973</v>
+        <v>6987424</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129373473</v>
+        <v>129373410</v>
       </c>
       <c r="B15" t="n">
-        <v>88992</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663293</v>
+        <v>663058</v>
       </c>
       <c r="R15" t="n">
-        <v>6987424</v>
+        <v>6986973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129373460</v>
+        <v>129373425</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>79148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>663293</v>
+        <v>663240</v>
       </c>
       <c r="R17" t="n">
-        <v>6987423</v>
+        <v>6987407</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129373455</v>
+        <v>129373460</v>
       </c>
       <c r="B18" t="n">
         <v>79081</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>663366</v>
+        <v>663293</v>
       </c>
       <c r="R18" t="n">
-        <v>6987548</v>
+        <v>6987423</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129373425</v>
+        <v>129373455</v>
       </c>
       <c r="B19" t="n">
-        <v>79148</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>663240</v>
+        <v>663366</v>
       </c>
       <c r="R19" t="n">
-        <v>6987407</v>
+        <v>6987548</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
